--- a/results/02-2026/beta/contributions-02-2026.xlsx
+++ b/results/02-2026/beta/contributions-02-2026.xlsx
@@ -22544,7 +22544,7 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>1.99661674952811</v>
+        <v>1.43166074182057</v>
       </c>
       <c r="E226" t="n">
         <v>-0.188450438947078</v>
@@ -22607,7 +22607,7 @@
         <v>0.147544970104152</v>
       </c>
       <c r="Y226" t="n">
-        <v>1.94567536039587</v>
+        <v>1.38071935268833</v>
       </c>
       <c r="Z226" t="n">
         <v>-0.137509049814841</v>
@@ -22622,10 +22622,10 @@
         <v>0.788317040780609</v>
       </c>
       <c r="AD226" t="n">
-        <v>2.59648335136164</v>
+        <v>2.0315273436541</v>
       </c>
       <c r="AE226" t="n">
-        <v>0.357823332001175</v>
+        <v>0.21658433007429</v>
       </c>
     </row>
     <row r="227">
@@ -22639,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.302030413940792</v>
+        <v>-0.537147991671363</v>
       </c>
       <c r="E227" t="n">
         <v>-0.175946814023728</v>
@@ -22702,7 +22702,7 @@
         <v>0.1559692344407</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.386255918035279</v>
+        <v>-0.621373495765851</v>
       </c>
       <c r="Z227" t="n">
         <v>-0.0917213099292404</v>
@@ -22717,10 +22717,10 @@
         <v>0.549179232509783</v>
       </c>
       <c r="AD227" t="n">
-        <v>0.0712020045452636</v>
+        <v>-0.163915573185308</v>
       </c>
       <c r="AE227" t="n">
-        <v>0.484021572084565</v>
+        <v>0.284003175725037</v>
       </c>
     </row>
     <row r="228">
@@ -22734,7 +22734,7 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.251312652171895</v>
+        <v>-0.271584709671224</v>
       </c>
       <c r="E228" t="n">
         <v>-0.174807656662485</v>
@@ -22797,7 +22797,7 @@
         <v>0.100316921437573</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.287441694670442</v>
+        <v>-0.30771375216977</v>
       </c>
       <c r="Z228" t="n">
         <v>-0.138678614163938</v>
@@ -22812,10 +22812,10 @@
         <v>0.446221183048196</v>
       </c>
       <c r="AD228" t="n">
-        <v>0.0201008742138161</v>
+        <v>-0.000171183285512244</v>
       </c>
       <c r="AE228" t="n">
-        <v>0.414229503763454</v>
+        <v>0.209143093029094</v>
       </c>
     </row>
     <row r="229">
@@ -22829,7 +22829,7 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.111201028942794</v>
+        <v>-0.108069522500618</v>
       </c>
       <c r="E229" t="n">
         <v>-0.198325825071049</v>
@@ -22892,7 +22892,7 @@
         <v>0.0533796470777238</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.170066418845336</v>
+        <v>-0.16693491240316</v>
       </c>
       <c r="Z229" t="n">
         <v>-0.139460435168507</v>
@@ -22907,10 +22907,10 @@
         <v>0.294278037089854</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.0152488169239894</v>
+        <v>-0.0121173104818139</v>
       </c>
       <c r="AE229" t="n">
-        <v>0.668134353299183</v>
+        <v>0.463830819175367</v>
       </c>
     </row>
     <row r="230">
@@ -22924,7 +22924,7 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.118588000564393</v>
+        <v>-0.115248471323857</v>
       </c>
       <c r="E230" t="n">
         <v>-0.184705112342636</v>
@@ -22987,7 +22987,7 @@
         <v>0.0311335267282681</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.164622415572112</v>
+        <v>-0.161282886331576</v>
       </c>
       <c r="Z230" t="n">
         <v>-0.138670697334917</v>
@@ -23002,10 +23002,10 @@
         <v>-0.309320568005882</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.612613680912911</v>
+        <v>-0.609274151672375</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.134139904769455</v>
+        <v>-0.196369554656252</v>
       </c>
     </row>
     <row r="231">
@@ -23019,7 +23019,7 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.10147567956618</v>
+        <v>-0.0986180464371817</v>
       </c>
       <c r="E231" t="n">
         <v>-0.179276164652479</v>
@@ -23082,7 +23082,7 @@
         <v>0.0212389044583038</v>
       </c>
       <c r="Y231" t="n">
-        <v>-0.1458144575889</v>
+        <v>-0.142956824459902</v>
       </c>
       <c r="Z231" t="n">
         <v>-0.134937386629759</v>
@@ -23097,10 +23097,10 @@
         <v>-0.320809097128814</v>
       </c>
       <c r="AD231" t="n">
-        <v>-0.601560941347473</v>
+        <v>-0.598703308218475</v>
       </c>
       <c r="AE231" t="n">
-        <v>-0.302330641242639</v>
+        <v>-0.305066488414544</v>
       </c>
     </row>
     <row r="232">
@@ -23114,7 +23114,7 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.108369739020907</v>
+        <v>-0.105317963879012</v>
       </c>
       <c r="E232" t="n">
         <v>-0.186499084275908</v>
@@ -23177,7 +23177,7 @@
         <v>0.00388762080915746</v>
       </c>
       <c r="Y232" t="n">
-        <v>-0.151029293519021</v>
+        <v>-0.147977518377125</v>
       </c>
       <c r="Z232" t="n">
         <v>-0.143839529777795</v>
@@ -23192,10 +23192,10 @@
         <v>-0.225147982341738</v>
       </c>
       <c r="AD232" t="n">
-        <v>-0.520016805638554</v>
+        <v>-0.516965030496658</v>
       </c>
       <c r="AE232" t="n">
-        <v>-0.437360061205732</v>
+        <v>-0.43426495021733</v>
       </c>
     </row>
     <row r="233">
@@ -23209,7 +23209,7 @@
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.178956498706162</v>
+        <v>-0.173916946159793</v>
       </c>
       <c r="E233" t="n">
         <v>-0.182999695185691</v>
@@ -23272,7 +23272,7 @@
         <v>-0.0152151749261088</v>
       </c>
       <c r="Y233" t="n">
-        <v>-0.220198903783034</v>
+        <v>-0.215159351236665</v>
       </c>
       <c r="Z233" t="n">
         <v>-0.14175729010882</v>
@@ -23287,10 +23287,10 @@
         <v>-0.287277273663092</v>
       </c>
       <c r="AD233" t="n">
-        <v>-0.649233467554946</v>
+        <v>-0.644193915008577</v>
       </c>
       <c r="AE233" t="n">
-        <v>-0.595856223863471</v>
+        <v>-0.592284101349021</v>
       </c>
     </row>
     <row r="234">
@@ -23304,7 +23304,7 @@
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>-6.38118745035198</v>
+        <v>-6.20148830728212</v>
       </c>
       <c r="E234" t="n">
         <v>-10.7880078888846</v>
@@ -23367,7 +23367,7 @@
         <v>-1.16887657204751</v>
       </c>
       <c r="Y234" t="n">
-        <v>-7.88235169895944</v>
+        <v>-7.70265255588958</v>
       </c>
       <c r="Z234" t="n">
         <v>-9.28684364027715</v>
@@ -23382,10 +23382,10 @@
         <v>-3.59449565957694</v>
       </c>
       <c r="AD234" t="n">
-        <v>-20.7636909988135</v>
+        <v>-20.5839918557437</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.63362555333863</v>
+        <v>-5.58596352736685</v>
       </c>
     </row>
     <row r="235">
@@ -23480,7 +23480,7 @@
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>-5.48323531800176</v>
+        <v>-5.43628770031223</v>
       </c>
     </row>
     <row r="236">
@@ -23575,7 +23575,7 @@
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>-5.35323111659212</v>
+        <v>-5.30704644268806</v>
       </c>
     </row>
     <row r="237">
@@ -23670,7 +23670,7 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>-5.19092274970338</v>
+        <v>-5.14599796393592</v>
       </c>
     </row>
     <row r="238">
@@ -23765,7 +23765,7 @@
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="239">
@@ -23860,7 +23860,7 @@
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="240">
@@ -23955,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="241">
@@ -24050,7 +24050,7 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="242">
@@ -24145,7 +24145,7 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="243">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="244">
@@ -24335,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="245">
@@ -24430,7 +24430,7 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="246">
@@ -24525,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="247">
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
   </sheetData>
